--- a/experiment/DAT+CNN_2CH_bestx4/Collect/DAT_Collect.xlsx
+++ b/experiment/DAT+CNN_2CH_bestx4/Collect/DAT_Collect.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gama\Desktop\New folder\DAT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F5C5AD2-8DA5-4982-BDBA-2903AEC4EBA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7368DF36-F745-4321-94C2-E45FBF8EA456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -397,10 +397,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F407"/>
+  <dimension ref="A1:F411"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -6424,133 +6425,2204 @@
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="E302" s="2"/>
-    </row>
-    <row r="305" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D305" s="2"/>
-      <c r="E305" s="2"/>
-    </row>
-    <row r="306" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C306" s="2"/>
-    </row>
-    <row r="309" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="F309" s="2"/>
-    </row>
-    <row r="311" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C311" s="2"/>
-      <c r="D311" s="2"/>
-    </row>
-    <row r="312" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B312" s="2"/>
-      <c r="D312" s="2"/>
-    </row>
-    <row r="313" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B313" s="2"/>
-    </row>
-    <row r="316" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B316" s="2"/>
-    </row>
-    <row r="319" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D319" s="2"/>
-    </row>
-    <row r="320" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E320" s="2"/>
-    </row>
-    <row r="321" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B321" s="2"/>
-      <c r="C321" s="2"/>
-      <c r="F321" s="2"/>
-    </row>
-    <row r="326" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C326" s="2"/>
-    </row>
-    <row r="327" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B327" s="2"/>
-      <c r="E327" s="2"/>
-    </row>
-    <row r="330" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D330" s="2"/>
-    </row>
-    <row r="331" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="F331" s="2"/>
-    </row>
-    <row r="332" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="F332" s="2"/>
-    </row>
-    <row r="335" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D335" s="2"/>
-    </row>
-    <row r="336" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C336" s="2"/>
-    </row>
-    <row r="339" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D339" s="2"/>
-    </row>
-    <row r="343" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E343" s="2"/>
-    </row>
-    <row r="344" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B344" s="2"/>
-    </row>
-    <row r="346" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="F346" s="2"/>
-    </row>
-    <row r="348" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C348" s="2"/>
-    </row>
-    <row r="349" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D349" s="2"/>
-    </row>
-    <row r="353" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B353" s="2"/>
-      <c r="E353" s="2"/>
-    </row>
-    <row r="354" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D354" s="2"/>
-      <c r="E354" s="2"/>
-    </row>
-    <row r="357" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C357" s="2"/>
-    </row>
-    <row r="361" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E361" s="3"/>
-      <c r="F361" s="2"/>
-    </row>
-    <row r="364" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D364" s="2"/>
-      <c r="F364" s="2"/>
-    </row>
-    <row r="366" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D366" s="2"/>
-      <c r="F366" s="2"/>
-    </row>
-    <row r="370" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D370" s="3"/>
-    </row>
-    <row r="375" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="F375" s="2"/>
-    </row>
-    <row r="378" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="F378" s="2"/>
-    </row>
-    <row r="379" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B379" s="2"/>
-      <c r="F379" s="3"/>
-    </row>
-    <row r="381" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C381" s="3"/>
-    </row>
-    <row r="390" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B390" s="2"/>
-    </row>
-    <row r="392" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D392" s="2"/>
-    </row>
-    <row r="395" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D395" s="2"/>
-    </row>
-    <row r="407" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B407" s="3"/>
+      <c r="A302">
+        <v>301</v>
+      </c>
+      <c r="B302">
+        <v>32.758000000000003</v>
+      </c>
+      <c r="C302">
+        <v>32.531999999999996</v>
+      </c>
+      <c r="D302">
+        <v>32.47</v>
+      </c>
+      <c r="E302" s="2">
+        <v>32.606999999999999</v>
+      </c>
+      <c r="F302">
+        <v>32.494</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A303">
+        <v>302</v>
+      </c>
+      <c r="B303">
+        <v>32.752000000000002</v>
+      </c>
+      <c r="C303">
+        <v>32.558</v>
+      </c>
+      <c r="D303">
+        <v>32.466999999999999</v>
+      </c>
+      <c r="E303">
+        <v>32.603999999999999</v>
+      </c>
+      <c r="F303">
+        <v>32.488999999999997</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A304">
+        <v>303</v>
+      </c>
+      <c r="B304">
+        <v>32.765000000000001</v>
+      </c>
+      <c r="C304">
+        <v>32.537999999999997</v>
+      </c>
+      <c r="D304">
+        <v>32.466000000000001</v>
+      </c>
+      <c r="E304">
+        <v>32.604999999999997</v>
+      </c>
+      <c r="F304">
+        <v>32.537999999999997</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A305">
+        <v>304</v>
+      </c>
+      <c r="B305">
+        <v>32.749000000000002</v>
+      </c>
+      <c r="C305">
+        <v>32.554000000000002</v>
+      </c>
+      <c r="D305" s="2">
+        <v>32.494999999999997</v>
+      </c>
+      <c r="E305" s="2">
+        <v>32.622</v>
+      </c>
+      <c r="F305">
+        <v>32.524000000000001</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A306">
+        <v>305</v>
+      </c>
+      <c r="B306">
+        <v>32.753999999999998</v>
+      </c>
+      <c r="C306" s="2">
+        <v>32.576999999999998</v>
+      </c>
+      <c r="D306">
+        <v>32.485999999999997</v>
+      </c>
+      <c r="E306">
+        <v>32.606000000000002</v>
+      </c>
+      <c r="F306">
+        <v>32.520000000000003</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A307">
+        <v>306</v>
+      </c>
+      <c r="B307">
+        <v>32.756</v>
+      </c>
+      <c r="C307">
+        <v>32.549999999999997</v>
+      </c>
+      <c r="D307">
+        <v>32.49</v>
+      </c>
+      <c r="E307">
+        <v>32.604999999999997</v>
+      </c>
+      <c r="F307">
+        <v>32.533999999999999</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A308">
+        <v>307</v>
+      </c>
+      <c r="B308">
+        <v>32.756</v>
+      </c>
+      <c r="C308">
+        <v>32.561999999999998</v>
+      </c>
+      <c r="D308">
+        <v>32.478000000000002</v>
+      </c>
+      <c r="E308">
+        <v>32.610999999999997</v>
+      </c>
+      <c r="F308">
+        <v>32.533999999999999</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A309">
+        <v>308</v>
+      </c>
+      <c r="B309">
+        <v>32.759</v>
+      </c>
+      <c r="C309">
+        <v>32.561</v>
+      </c>
+      <c r="D309">
+        <v>32.466999999999999</v>
+      </c>
+      <c r="E309">
+        <v>32.616</v>
+      </c>
+      <c r="F309" s="2">
+        <v>32.552999999999997</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A310">
+        <v>309</v>
+      </c>
+      <c r="B310">
+        <v>32.76</v>
+      </c>
+      <c r="C310">
+        <v>32.567</v>
+      </c>
+      <c r="D310">
+        <v>32.478000000000002</v>
+      </c>
+      <c r="E310">
+        <v>32.613999999999997</v>
+      </c>
+      <c r="F310">
+        <v>32.54</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A311">
+        <v>310</v>
+      </c>
+      <c r="B311">
+        <v>32.758000000000003</v>
+      </c>
+      <c r="C311" s="2">
+        <v>32.576999999999998</v>
+      </c>
+      <c r="D311" s="2">
+        <v>32.496000000000002</v>
+      </c>
+      <c r="E311">
+        <v>32.607999999999997</v>
+      </c>
+      <c r="F311">
+        <v>32.530999999999999</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A312">
+        <v>311</v>
+      </c>
+      <c r="B312" s="2">
+        <v>32.771999999999998</v>
+      </c>
+      <c r="C312">
+        <v>32.552999999999997</v>
+      </c>
+      <c r="D312" s="2">
+        <v>32.511000000000003</v>
+      </c>
+      <c r="E312">
+        <v>32.601999999999997</v>
+      </c>
+      <c r="F312">
+        <v>32.534999999999997</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A313">
+        <v>312</v>
+      </c>
+      <c r="B313" s="2">
+        <v>32.771999999999998</v>
+      </c>
+      <c r="C313">
+        <v>32.531999999999996</v>
+      </c>
+      <c r="D313">
+        <v>32.485999999999997</v>
+      </c>
+      <c r="E313">
+        <v>32.603999999999999</v>
+      </c>
+      <c r="F313">
+        <v>32.520000000000003</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A314">
+        <v>313</v>
+      </c>
+      <c r="B314">
+        <v>32.762999999999998</v>
+      </c>
+      <c r="C314">
+        <v>32.552999999999997</v>
+      </c>
+      <c r="D314">
+        <v>32.503</v>
+      </c>
+      <c r="E314">
+        <v>32.606000000000002</v>
+      </c>
+      <c r="F314">
+        <v>32.539000000000001</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A315">
+        <v>314</v>
+      </c>
+      <c r="B315">
+        <v>32.755000000000003</v>
+      </c>
+      <c r="C315">
+        <v>32.548000000000002</v>
+      </c>
+      <c r="D315">
+        <v>32.502000000000002</v>
+      </c>
+      <c r="E315">
+        <v>32.61</v>
+      </c>
+      <c r="F315">
+        <v>32.548000000000002</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A316">
+        <v>315</v>
+      </c>
+      <c r="B316" s="2">
+        <v>32.777000000000001</v>
+      </c>
+      <c r="C316">
+        <v>32.552999999999997</v>
+      </c>
+      <c r="D316">
+        <v>32.500999999999998</v>
+      </c>
+      <c r="E316">
+        <v>32.610999999999997</v>
+      </c>
+      <c r="F316">
+        <v>32.534999999999997</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A317">
+        <v>316</v>
+      </c>
+      <c r="B317">
+        <v>32.767000000000003</v>
+      </c>
+      <c r="C317">
+        <v>32.563000000000002</v>
+      </c>
+      <c r="D317">
+        <v>32.491</v>
+      </c>
+      <c r="E317">
+        <v>32.610999999999997</v>
+      </c>
+      <c r="F317">
+        <v>32.531999999999996</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A318">
+        <v>317</v>
+      </c>
+      <c r="B318">
+        <v>32.761000000000003</v>
+      </c>
+      <c r="C318">
+        <v>32.576000000000001</v>
+      </c>
+      <c r="D318">
+        <v>32.479999999999997</v>
+      </c>
+      <c r="E318">
+        <v>32.607999999999997</v>
+      </c>
+      <c r="F318">
+        <v>32.546999999999997</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A319">
+        <v>318</v>
+      </c>
+      <c r="B319">
+        <v>32.753</v>
+      </c>
+      <c r="C319">
+        <v>32.552999999999997</v>
+      </c>
+      <c r="D319" s="2">
+        <v>32.511000000000003</v>
+      </c>
+      <c r="E319">
+        <v>32.607999999999997</v>
+      </c>
+      <c r="F319">
+        <v>32.543999999999997</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A320">
+        <v>319</v>
+      </c>
+      <c r="B320">
+        <v>32.771999999999998</v>
+      </c>
+      <c r="C320">
+        <v>32.57</v>
+      </c>
+      <c r="D320">
+        <v>32.497999999999998</v>
+      </c>
+      <c r="E320" s="2">
+        <v>32.624000000000002</v>
+      </c>
+      <c r="F320">
+        <v>32.520000000000003</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A321">
+        <v>320</v>
+      </c>
+      <c r="B321" s="2">
+        <v>32.777999999999999</v>
+      </c>
+      <c r="C321" s="2">
+        <v>32.578000000000003</v>
+      </c>
+      <c r="D321">
+        <v>32.494</v>
+      </c>
+      <c r="E321">
+        <v>32.616</v>
+      </c>
+      <c r="F321" s="2">
+        <v>32.558</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A322">
+        <v>321</v>
+      </c>
+      <c r="B322">
+        <v>32.771000000000001</v>
+      </c>
+      <c r="C322">
+        <v>32.57</v>
+      </c>
+      <c r="D322">
+        <v>32.494</v>
+      </c>
+      <c r="E322">
+        <v>32.618000000000002</v>
+      </c>
+      <c r="F322">
+        <v>32.534999999999997</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A323">
+        <v>322</v>
+      </c>
+      <c r="B323">
+        <v>32.771000000000001</v>
+      </c>
+      <c r="C323">
+        <v>32.575000000000003</v>
+      </c>
+      <c r="D323">
+        <v>32.499000000000002</v>
+      </c>
+      <c r="E323">
+        <v>32.624000000000002</v>
+      </c>
+      <c r="F323">
+        <v>32.543999999999997</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A324">
+        <v>323</v>
+      </c>
+      <c r="B324">
+        <v>32.768999999999998</v>
+      </c>
+      <c r="C324">
+        <v>32.563000000000002</v>
+      </c>
+      <c r="D324">
+        <v>32.491</v>
+      </c>
+      <c r="E324">
+        <v>32.622999999999998</v>
+      </c>
+      <c r="F324">
+        <v>32.551000000000002</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A325">
+        <v>324</v>
+      </c>
+      <c r="B325">
+        <v>32.750999999999998</v>
+      </c>
+      <c r="C325">
+        <v>32.551000000000002</v>
+      </c>
+      <c r="D325">
+        <v>32.494999999999997</v>
+      </c>
+      <c r="E325">
+        <v>32.621000000000002</v>
+      </c>
+      <c r="F325">
+        <v>32.557000000000002</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A326">
+        <v>325</v>
+      </c>
+      <c r="B326">
+        <v>32.72</v>
+      </c>
+      <c r="C326" s="2">
+        <v>32.584000000000003</v>
+      </c>
+      <c r="D326">
+        <v>32.51</v>
+      </c>
+      <c r="E326">
+        <v>32.624000000000002</v>
+      </c>
+      <c r="F326">
+        <v>32.540999999999997</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A327">
+        <v>326</v>
+      </c>
+      <c r="B327" s="2">
+        <v>32.783000000000001</v>
+      </c>
+      <c r="C327">
+        <v>32.572000000000003</v>
+      </c>
+      <c r="D327">
+        <v>32.505000000000003</v>
+      </c>
+      <c r="E327" s="2">
+        <v>32.631999999999998</v>
+      </c>
+      <c r="F327">
+        <v>32.554000000000002</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A328">
+        <v>327</v>
+      </c>
+      <c r="B328">
+        <v>32.780999999999999</v>
+      </c>
+      <c r="C328">
+        <v>32.576999999999998</v>
+      </c>
+      <c r="D328">
+        <v>32.494999999999997</v>
+      </c>
+      <c r="E328">
+        <v>32.630000000000003</v>
+      </c>
+      <c r="F328">
+        <v>32.549999999999997</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A329">
+        <v>328</v>
+      </c>
+      <c r="B329">
+        <v>32.76</v>
+      </c>
+      <c r="C329">
+        <v>32.581000000000003</v>
+      </c>
+      <c r="D329">
+        <v>32.506</v>
+      </c>
+      <c r="E329">
+        <v>32.622999999999998</v>
+      </c>
+      <c r="F329">
+        <v>32.557000000000002</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A330">
+        <v>329</v>
+      </c>
+      <c r="B330">
+        <v>32.774000000000001</v>
+      </c>
+      <c r="C330">
+        <v>32.576000000000001</v>
+      </c>
+      <c r="D330" s="2">
+        <v>32.511000000000003</v>
+      </c>
+      <c r="E330">
+        <v>32.625999999999998</v>
+      </c>
+      <c r="F330">
+        <v>32.545000000000002</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A331">
+        <v>330</v>
+      </c>
+      <c r="B331">
+        <v>32.767000000000003</v>
+      </c>
+      <c r="C331">
+        <v>32.575000000000003</v>
+      </c>
+      <c r="D331">
+        <v>32.508000000000003</v>
+      </c>
+      <c r="E331">
+        <v>32.627000000000002</v>
+      </c>
+      <c r="F331" s="2">
+        <v>32.56</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A332">
+        <v>331</v>
+      </c>
+      <c r="B332">
+        <v>32.755000000000003</v>
+      </c>
+      <c r="C332">
+        <v>32.569000000000003</v>
+      </c>
+      <c r="D332">
+        <v>32.51</v>
+      </c>
+      <c r="E332">
+        <v>32.616</v>
+      </c>
+      <c r="F332" s="2">
+        <v>32.564999999999998</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A333">
+        <v>332</v>
+      </c>
+      <c r="B333">
+        <v>32.768000000000001</v>
+      </c>
+      <c r="C333">
+        <v>32.58</v>
+      </c>
+      <c r="D333">
+        <v>32.51</v>
+      </c>
+      <c r="E333">
+        <v>32.603999999999999</v>
+      </c>
+      <c r="F333">
+        <v>32.557000000000002</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A334">
+        <v>333</v>
+      </c>
+      <c r="B334">
+        <v>32.765999999999998</v>
+      </c>
+      <c r="C334">
+        <v>32.551000000000002</v>
+      </c>
+      <c r="D334">
+        <v>32.506</v>
+      </c>
+      <c r="E334">
+        <v>32.616</v>
+      </c>
+      <c r="F334">
+        <v>32.549999999999997</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A335">
+        <v>334</v>
+      </c>
+      <c r="B335">
+        <v>32.76</v>
+      </c>
+      <c r="C335">
+        <v>32.575000000000003</v>
+      </c>
+      <c r="D335" s="2">
+        <v>32.512999999999998</v>
+      </c>
+      <c r="E335">
+        <v>32.624000000000002</v>
+      </c>
+      <c r="F335">
+        <v>32.554000000000002</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A336">
+        <v>335</v>
+      </c>
+      <c r="B336">
+        <v>32.762999999999998</v>
+      </c>
+      <c r="C336" s="2">
+        <v>32.588999999999999</v>
+      </c>
+      <c r="D336">
+        <v>32.508000000000003</v>
+      </c>
+      <c r="E336">
+        <v>32.627000000000002</v>
+      </c>
+      <c r="F336">
+        <v>32.564999999999998</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A337">
+        <v>336</v>
+      </c>
+      <c r="B337">
+        <v>32.768000000000001</v>
+      </c>
+      <c r="C337">
+        <v>32.58</v>
+      </c>
+      <c r="D337">
+        <v>32.512</v>
+      </c>
+      <c r="E337">
+        <v>32.628</v>
+      </c>
+      <c r="F337">
+        <v>32.545999999999999</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A338">
+        <v>337</v>
+      </c>
+      <c r="B338">
+        <v>32.767000000000003</v>
+      </c>
+      <c r="C338">
+        <v>32.576999999999998</v>
+      </c>
+      <c r="D338">
+        <v>32.503999999999998</v>
+      </c>
+      <c r="E338">
+        <v>32.622999999999998</v>
+      </c>
+      <c r="F338">
+        <v>32.533999999999999</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A339">
+        <v>338</v>
+      </c>
+      <c r="B339">
+        <v>32.765000000000001</v>
+      </c>
+      <c r="C339">
+        <v>32.563000000000002</v>
+      </c>
+      <c r="D339" s="2">
+        <v>32.523000000000003</v>
+      </c>
+      <c r="E339">
+        <v>32.616</v>
+      </c>
+      <c r="F339">
+        <v>32.552</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A340">
+        <v>339</v>
+      </c>
+      <c r="B340">
+        <v>32.738999999999997</v>
+      </c>
+      <c r="C340">
+        <v>32.570999999999998</v>
+      </c>
+      <c r="D340">
+        <v>32.515000000000001</v>
+      </c>
+      <c r="E340">
+        <v>32.619</v>
+      </c>
+      <c r="F340">
+        <v>32.54</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A341">
+        <v>340</v>
+      </c>
+      <c r="B341">
+        <v>32.773000000000003</v>
+      </c>
+      <c r="C341">
+        <v>32.581000000000003</v>
+      </c>
+      <c r="D341">
+        <v>32.505000000000003</v>
+      </c>
+      <c r="E341">
+        <v>32.624000000000002</v>
+      </c>
+      <c r="F341">
+        <v>32.545000000000002</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A342">
+        <v>341</v>
+      </c>
+      <c r="B342">
+        <v>32.731999999999999</v>
+      </c>
+      <c r="C342">
+        <v>32.567999999999998</v>
+      </c>
+      <c r="D342">
+        <v>32.506</v>
+      </c>
+      <c r="E342">
+        <v>32.619999999999997</v>
+      </c>
+      <c r="F342">
+        <v>32.555</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A343">
+        <v>342</v>
+      </c>
+      <c r="B343">
+        <v>32.752000000000002</v>
+      </c>
+      <c r="C343">
+        <v>32.582999999999998</v>
+      </c>
+      <c r="D343">
+        <v>32.51</v>
+      </c>
+      <c r="E343" s="2">
+        <v>32.631999999999998</v>
+      </c>
+      <c r="F343">
+        <v>32.561</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A344">
+        <v>343</v>
+      </c>
+      <c r="B344" s="2">
+        <v>32.786999999999999</v>
+      </c>
+      <c r="C344">
+        <v>32.572000000000003</v>
+      </c>
+      <c r="D344">
+        <v>32.521000000000001</v>
+      </c>
+      <c r="E344">
+        <v>32.628999999999998</v>
+      </c>
+      <c r="F344">
+        <v>32.555</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A345">
+        <v>344</v>
+      </c>
+      <c r="B345">
+        <v>32.758000000000003</v>
+      </c>
+      <c r="C345">
+        <v>32.573999999999998</v>
+      </c>
+      <c r="D345">
+        <v>32.521999999999998</v>
+      </c>
+      <c r="E345">
+        <v>32.624000000000002</v>
+      </c>
+      <c r="F345">
+        <v>32.561999999999998</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A346">
+        <v>345</v>
+      </c>
+      <c r="B346">
+        <v>32.777999999999999</v>
+      </c>
+      <c r="C346">
+        <v>32.569000000000003</v>
+      </c>
+      <c r="D346">
+        <v>32.518999999999998</v>
+      </c>
+      <c r="E346">
+        <v>32.624000000000002</v>
+      </c>
+      <c r="F346" s="2">
+        <v>32.572000000000003</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A347">
+        <v>346</v>
+      </c>
+      <c r="B347">
+        <v>32.768000000000001</v>
+      </c>
+      <c r="C347">
+        <v>32.58</v>
+      </c>
+      <c r="D347">
+        <v>32.518000000000001</v>
+      </c>
+      <c r="E347">
+        <v>32.625</v>
+      </c>
+      <c r="F347">
+        <v>32.563000000000002</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A348">
+        <v>347</v>
+      </c>
+      <c r="B348">
+        <v>32.764000000000003</v>
+      </c>
+      <c r="C348" s="2">
+        <v>32.590000000000003</v>
+      </c>
+      <c r="D348">
+        <v>32.515999999999998</v>
+      </c>
+      <c r="E348">
+        <v>32.625</v>
+      </c>
+      <c r="F348">
+        <v>32.561999999999998</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A349">
+        <v>348</v>
+      </c>
+      <c r="B349">
+        <v>32.756999999999998</v>
+      </c>
+      <c r="C349">
+        <v>32.570999999999998</v>
+      </c>
+      <c r="D349" s="2">
+        <v>32.527000000000001</v>
+      </c>
+      <c r="E349">
+        <v>32.622999999999998</v>
+      </c>
+      <c r="F349">
+        <v>32.558999999999997</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A350">
+        <v>349</v>
+      </c>
+      <c r="B350">
+        <v>32.762</v>
+      </c>
+      <c r="C350">
+        <v>32.582999999999998</v>
+      </c>
+      <c r="D350">
+        <v>32.515999999999998</v>
+      </c>
+      <c r="E350">
+        <v>32.628</v>
+      </c>
+      <c r="F350">
+        <v>32.558</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A351">
+        <v>350</v>
+      </c>
+      <c r="B351">
+        <v>32.781999999999996</v>
+      </c>
+      <c r="C351">
+        <v>32.581000000000003</v>
+      </c>
+      <c r="D351">
+        <v>32.515000000000001</v>
+      </c>
+      <c r="E351">
+        <v>32.625</v>
+      </c>
+      <c r="F351">
+        <v>32.557000000000002</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A352">
+        <v>351</v>
+      </c>
+      <c r="B352">
+        <v>32.78</v>
+      </c>
+      <c r="C352">
+        <v>32.575000000000003</v>
+      </c>
+      <c r="D352">
+        <v>32.515999999999998</v>
+      </c>
+      <c r="E352">
+        <v>32.625</v>
+      </c>
+      <c r="F352">
+        <v>32.564</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A353">
+        <v>352</v>
+      </c>
+      <c r="B353" s="2">
+        <v>32.792999999999999</v>
+      </c>
+      <c r="C353">
+        <v>32.581000000000003</v>
+      </c>
+      <c r="D353">
+        <v>32.521999999999998</v>
+      </c>
+      <c r="E353" s="2">
+        <v>32.637</v>
+      </c>
+      <c r="F353">
+        <v>32.567999999999998</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A354">
+        <v>353</v>
+      </c>
+      <c r="B354">
+        <v>32.784999999999997</v>
+      </c>
+      <c r="C354">
+        <v>32.581000000000003</v>
+      </c>
+      <c r="D354" s="2">
+        <v>32.53</v>
+      </c>
+      <c r="E354" s="2">
+        <v>32.639000000000003</v>
+      </c>
+      <c r="F354">
+        <v>32.570999999999998</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A355">
+        <v>354</v>
+      </c>
+      <c r="B355">
+        <v>32.768999999999998</v>
+      </c>
+      <c r="C355">
+        <v>32.585999999999999</v>
+      </c>
+      <c r="D355">
+        <v>32.523000000000003</v>
+      </c>
+      <c r="E355">
+        <v>32.636000000000003</v>
+      </c>
+      <c r="F355">
+        <v>32.570999999999998</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A356">
+        <v>355</v>
+      </c>
+      <c r="B356">
+        <v>32.774000000000001</v>
+      </c>
+      <c r="C356">
+        <v>32.582000000000001</v>
+      </c>
+      <c r="D356">
+        <v>32.524999999999999</v>
+      </c>
+      <c r="E356">
+        <v>32.628</v>
+      </c>
+      <c r="F356">
+        <v>32.555</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A357">
+        <v>356</v>
+      </c>
+      <c r="B357">
+        <v>32.771999999999998</v>
+      </c>
+      <c r="C357" s="2">
+        <v>32.593000000000004</v>
+      </c>
+      <c r="D357">
+        <v>32.529000000000003</v>
+      </c>
+      <c r="E357">
+        <v>32.634</v>
+      </c>
+      <c r="F357">
+        <v>32.57</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A358">
+        <v>357</v>
+      </c>
+      <c r="B358">
+        <v>32.776000000000003</v>
+      </c>
+      <c r="C358">
+        <v>32.584000000000003</v>
+      </c>
+      <c r="D358">
+        <v>32.517000000000003</v>
+      </c>
+      <c r="E358">
+        <v>32.628999999999998</v>
+      </c>
+      <c r="F358">
+        <v>32.566000000000003</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A359">
+        <v>358</v>
+      </c>
+      <c r="B359">
+        <v>32.768999999999998</v>
+      </c>
+      <c r="C359">
+        <v>32.584000000000003</v>
+      </c>
+      <c r="D359">
+        <v>32.53</v>
+      </c>
+      <c r="E359">
+        <v>32.636000000000003</v>
+      </c>
+      <c r="F359">
+        <v>32.566000000000003</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A360">
+        <v>359</v>
+      </c>
+      <c r="B360">
+        <v>32.786999999999999</v>
+      </c>
+      <c r="C360">
+        <v>32.585999999999999</v>
+      </c>
+      <c r="D360">
+        <v>32.518999999999998</v>
+      </c>
+      <c r="E360">
+        <v>32.633000000000003</v>
+      </c>
+      <c r="F360">
+        <v>32.564999999999998</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A361">
+        <v>360</v>
+      </c>
+      <c r="B361">
+        <v>32.79</v>
+      </c>
+      <c r="C361">
+        <v>32.579000000000001</v>
+      </c>
+      <c r="D361">
+        <v>32.521999999999998</v>
+      </c>
+      <c r="E361" s="3">
+        <v>32.652000000000001</v>
+      </c>
+      <c r="F361" s="2">
+        <v>32.572000000000003</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A362">
+        <v>361</v>
+      </c>
+      <c r="B362">
+        <v>32.765999999999998</v>
+      </c>
+      <c r="C362">
+        <v>32.573999999999998</v>
+      </c>
+      <c r="D362">
+        <v>32.527999999999999</v>
+      </c>
+      <c r="E362">
+        <v>32.628</v>
+      </c>
+      <c r="F362">
+        <v>32.564999999999998</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A363">
+        <v>362</v>
+      </c>
+      <c r="B363">
+        <v>32.777999999999999</v>
+      </c>
+      <c r="C363">
+        <v>32.585999999999999</v>
+      </c>
+      <c r="D363">
+        <v>32.526000000000003</v>
+      </c>
+      <c r="E363">
+        <v>32.643999999999998</v>
+      </c>
+      <c r="F363">
+        <v>32.57</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A364">
+        <v>363</v>
+      </c>
+      <c r="B364">
+        <v>32.783000000000001</v>
+      </c>
+      <c r="C364">
+        <v>32.57</v>
+      </c>
+      <c r="D364" s="2">
+        <v>32.531999999999996</v>
+      </c>
+      <c r="E364">
+        <v>32.637</v>
+      </c>
+      <c r="F364" s="2">
+        <v>32.573</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A365">
+        <v>364</v>
+      </c>
+      <c r="B365">
+        <v>32.789000000000001</v>
+      </c>
+      <c r="C365">
+        <v>32.579000000000001</v>
+      </c>
+      <c r="D365">
+        <v>32.531999999999996</v>
+      </c>
+      <c r="E365">
+        <v>32.640999999999998</v>
+      </c>
+      <c r="F365">
+        <v>32.569000000000003</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A366">
+        <v>365</v>
+      </c>
+      <c r="B366">
+        <v>32.777000000000001</v>
+      </c>
+      <c r="C366">
+        <v>32.590000000000003</v>
+      </c>
+      <c r="D366" s="2">
+        <v>32.534999999999997</v>
+      </c>
+      <c r="E366">
+        <v>32.642000000000003</v>
+      </c>
+      <c r="F366" s="2">
+        <v>32.575000000000003</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A367">
+        <v>366</v>
+      </c>
+      <c r="B367">
+        <v>32.784999999999997</v>
+      </c>
+      <c r="C367">
+        <v>32.578000000000003</v>
+      </c>
+      <c r="D367">
+        <v>32.527000000000001</v>
+      </c>
+      <c r="E367">
+        <v>32.645000000000003</v>
+      </c>
+      <c r="F367">
+        <v>32.567999999999998</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A368">
+        <v>367</v>
+      </c>
+      <c r="B368">
+        <v>32.774999999999999</v>
+      </c>
+      <c r="C368">
+        <v>32.584000000000003</v>
+      </c>
+      <c r="D368">
+        <v>32.524999999999999</v>
+      </c>
+      <c r="E368">
+        <v>32.643999999999998</v>
+      </c>
+      <c r="F368">
+        <v>32.561999999999998</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A369">
+        <v>368</v>
+      </c>
+      <c r="B369">
+        <v>32.781999999999996</v>
+      </c>
+      <c r="C369">
+        <v>32.587000000000003</v>
+      </c>
+      <c r="D369">
+        <v>32.526000000000003</v>
+      </c>
+      <c r="E369">
+        <v>32.642000000000003</v>
+      </c>
+      <c r="F369">
+        <v>32.566000000000003</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A370">
+        <v>369</v>
+      </c>
+      <c r="B370">
+        <v>32.784999999999997</v>
+      </c>
+      <c r="C370">
+        <v>32.58</v>
+      </c>
+      <c r="D370" s="3">
+        <v>32.536999999999999</v>
+      </c>
+      <c r="E370">
+        <v>32.642000000000003</v>
+      </c>
+      <c r="F370">
+        <v>32.57</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A371">
+        <v>370</v>
+      </c>
+      <c r="B371">
+        <v>32.789000000000001</v>
+      </c>
+      <c r="C371">
+        <v>32.58</v>
+      </c>
+      <c r="D371">
+        <v>32.531999999999996</v>
+      </c>
+      <c r="E371">
+        <v>32.643000000000001</v>
+      </c>
+      <c r="F371">
+        <v>32.57</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A372">
+        <v>371</v>
+      </c>
+      <c r="B372">
+        <v>32.78</v>
+      </c>
+      <c r="C372">
+        <v>32.582000000000001</v>
+      </c>
+      <c r="D372">
+        <v>32.524999999999999</v>
+      </c>
+      <c r="E372">
+        <v>32.645000000000003</v>
+      </c>
+      <c r="F372">
+        <v>32.570999999999998</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A373">
+        <v>372</v>
+      </c>
+      <c r="B373">
+        <v>32.784999999999997</v>
+      </c>
+      <c r="C373">
+        <v>32.587000000000003</v>
+      </c>
+      <c r="D373">
+        <v>32.527999999999999</v>
+      </c>
+      <c r="E373">
+        <v>32.645000000000003</v>
+      </c>
+      <c r="F373">
+        <v>32.572000000000003</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A374">
+        <v>373</v>
+      </c>
+      <c r="B374">
+        <v>32.786000000000001</v>
+      </c>
+      <c r="C374">
+        <v>32.58</v>
+      </c>
+      <c r="D374">
+        <v>32.527000000000001</v>
+      </c>
+      <c r="E374">
+        <v>32.637</v>
+      </c>
+      <c r="F374">
+        <v>32.569000000000003</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A375">
+        <v>374</v>
+      </c>
+      <c r="B375">
+        <v>32.792000000000002</v>
+      </c>
+      <c r="C375">
+        <v>32.585999999999999</v>
+      </c>
+      <c r="D375">
+        <v>32.531999999999996</v>
+      </c>
+      <c r="E375">
+        <v>32.64</v>
+      </c>
+      <c r="F375" s="2">
+        <v>32.575000000000003</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A376">
+        <v>375</v>
+      </c>
+      <c r="B376">
+        <v>32.789000000000001</v>
+      </c>
+      <c r="C376">
+        <v>32.58</v>
+      </c>
+      <c r="D376">
+        <v>32.533000000000001</v>
+      </c>
+      <c r="E376">
+        <v>32.645000000000003</v>
+      </c>
+      <c r="F376">
+        <v>32.573</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A377">
+        <v>376</v>
+      </c>
+      <c r="B377">
+        <v>32.779000000000003</v>
+      </c>
+      <c r="C377">
+        <v>32.587000000000003</v>
+      </c>
+      <c r="D377">
+        <v>32.530999999999999</v>
+      </c>
+      <c r="E377">
+        <v>32.640999999999998</v>
+      </c>
+      <c r="F377">
+        <v>32.566000000000003</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A378">
+        <v>377</v>
+      </c>
+      <c r="B378">
+        <v>32.78</v>
+      </c>
+      <c r="C378">
+        <v>32.582999999999998</v>
+      </c>
+      <c r="D378">
+        <v>32.526000000000003</v>
+      </c>
+      <c r="E378">
+        <v>32.643000000000001</v>
+      </c>
+      <c r="F378" s="2">
+        <v>32.576000000000001</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A379">
+        <v>378</v>
+      </c>
+      <c r="B379" s="2">
+        <v>32.793999999999997</v>
+      </c>
+      <c r="C379">
+        <v>32.590000000000003</v>
+      </c>
+      <c r="D379">
+        <v>32.53</v>
+      </c>
+      <c r="E379">
+        <v>32.646000000000001</v>
+      </c>
+      <c r="F379" s="3">
+        <v>32.579000000000001</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A380">
+        <v>379</v>
+      </c>
+      <c r="B380">
+        <v>32.789000000000001</v>
+      </c>
+      <c r="C380">
+        <v>32.578000000000003</v>
+      </c>
+      <c r="D380">
+        <v>32.53</v>
+      </c>
+      <c r="E380">
+        <v>32.64</v>
+      </c>
+      <c r="F380">
+        <v>32.573999999999998</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A381">
+        <v>380</v>
+      </c>
+      <c r="B381">
+        <v>32.780999999999999</v>
+      </c>
+      <c r="C381" s="3">
+        <v>32.597000000000001</v>
+      </c>
+      <c r="D381">
+        <v>32.533999999999999</v>
+      </c>
+      <c r="E381">
+        <v>32.639000000000003</v>
+      </c>
+      <c r="F381">
+        <v>32.572000000000003</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A382">
+        <v>381</v>
+      </c>
+      <c r="B382">
+        <v>32.777000000000001</v>
+      </c>
+      <c r="C382">
+        <v>32.585999999999999</v>
+      </c>
+      <c r="D382">
+        <v>32.53</v>
+      </c>
+      <c r="E382">
+        <v>32.646000000000001</v>
+      </c>
+      <c r="F382">
+        <v>32.575000000000003</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A383">
+        <v>382</v>
+      </c>
+      <c r="B383">
+        <v>32.793999999999997</v>
+      </c>
+      <c r="C383">
+        <v>32.593000000000004</v>
+      </c>
+      <c r="D383">
+        <v>32.531999999999996</v>
+      </c>
+      <c r="E383">
+        <v>32.643999999999998</v>
+      </c>
+      <c r="F383">
+        <v>32.566000000000003</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A384">
+        <v>383</v>
+      </c>
+      <c r="B384">
+        <v>32.793999999999997</v>
+      </c>
+      <c r="C384">
+        <v>32.587000000000003</v>
+      </c>
+      <c r="D384">
+        <v>32.530999999999999</v>
+      </c>
+      <c r="E384">
+        <v>32.642000000000003</v>
+      </c>
+      <c r="F384">
+        <v>32.567999999999998</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A385">
+        <v>384</v>
+      </c>
+      <c r="B385">
+        <v>32.792999999999999</v>
+      </c>
+      <c r="C385">
+        <v>32.587000000000003</v>
+      </c>
+      <c r="D385">
+        <v>32.533000000000001</v>
+      </c>
+      <c r="E385">
+        <v>32.645000000000003</v>
+      </c>
+      <c r="F385">
+        <v>32.572000000000003</v>
+      </c>
+    </row>
+    <row r="386" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A386">
+        <v>385</v>
+      </c>
+      <c r="B386">
+        <v>32.786999999999999</v>
+      </c>
+      <c r="C386">
+        <v>32.588999999999999</v>
+      </c>
+      <c r="D386">
+        <v>32.531999999999996</v>
+      </c>
+      <c r="E386">
+        <v>32.643999999999998</v>
+      </c>
+      <c r="F386">
+        <v>32.572000000000003</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A387">
+        <v>386</v>
+      </c>
+      <c r="B387">
+        <v>32.789000000000001</v>
+      </c>
+      <c r="C387">
+        <v>32.587000000000003</v>
+      </c>
+      <c r="D387">
+        <v>32.533999999999999</v>
+      </c>
+      <c r="E387">
+        <v>32.643999999999998</v>
+      </c>
+      <c r="F387">
+        <v>32.570999999999998</v>
+      </c>
+    </row>
+    <row r="388" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A388">
+        <v>387</v>
+      </c>
+      <c r="B388">
+        <v>32.774000000000001</v>
+      </c>
+      <c r="C388">
+        <v>32.594000000000001</v>
+      </c>
+      <c r="D388">
+        <v>32.533999999999999</v>
+      </c>
+      <c r="E388">
+        <v>32.640999999999998</v>
+      </c>
+      <c r="F388">
+        <v>32.576999999999998</v>
+      </c>
+    </row>
+    <row r="389" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A389">
+        <v>388</v>
+      </c>
+      <c r="B389">
+        <v>32.758000000000003</v>
+      </c>
+      <c r="C389">
+        <v>32.588999999999999</v>
+      </c>
+      <c r="D389">
+        <v>32.531999999999996</v>
+      </c>
+      <c r="E389">
+        <v>32.646000000000001</v>
+      </c>
+      <c r="F389">
+        <v>32.578000000000003</v>
+      </c>
+    </row>
+    <row r="390" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A390">
+        <v>389</v>
+      </c>
+      <c r="B390" s="2">
+        <v>32.802999999999997</v>
+      </c>
+      <c r="C390">
+        <v>32.588000000000001</v>
+      </c>
+      <c r="D390">
+        <v>32.534999999999997</v>
+      </c>
+      <c r="E390">
+        <v>32.646999999999998</v>
+      </c>
+      <c r="F390">
+        <v>32.570999999999998</v>
+      </c>
+    </row>
+    <row r="391" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A391">
+        <v>390</v>
+      </c>
+      <c r="B391">
+        <v>32.787999999999997</v>
+      </c>
+      <c r="C391">
+        <v>32.582999999999998</v>
+      </c>
+      <c r="D391">
+        <v>32.536000000000001</v>
+      </c>
+      <c r="E391">
+        <v>32.643999999999998</v>
+      </c>
+      <c r="F391">
+        <v>32.573</v>
+      </c>
+    </row>
+    <row r="392" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A392">
+        <v>391</v>
+      </c>
+      <c r="B392">
+        <v>32.777000000000001</v>
+      </c>
+      <c r="C392">
+        <v>32.588000000000001</v>
+      </c>
+      <c r="D392" s="2">
+        <v>32.536999999999999</v>
+      </c>
+      <c r="E392">
+        <v>32.646999999999998</v>
+      </c>
+      <c r="F392">
+        <v>32.572000000000003</v>
+      </c>
+    </row>
+    <row r="393" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A393">
+        <v>392</v>
+      </c>
+      <c r="B393">
+        <v>32.787999999999997</v>
+      </c>
+      <c r="C393">
+        <v>32.588999999999999</v>
+      </c>
+      <c r="D393">
+        <v>32.534999999999997</v>
+      </c>
+      <c r="E393">
+        <v>32.649000000000001</v>
+      </c>
+      <c r="F393">
+        <v>32.570999999999998</v>
+      </c>
+    </row>
+    <row r="394" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A394">
+        <v>393</v>
+      </c>
+      <c r="B394">
+        <v>32.789000000000001</v>
+      </c>
+      <c r="C394">
+        <v>32.585000000000001</v>
+      </c>
+      <c r="D394">
+        <v>32.533000000000001</v>
+      </c>
+      <c r="E394">
+        <v>32.648000000000003</v>
+      </c>
+      <c r="F394">
+        <v>32.573</v>
+      </c>
+    </row>
+    <row r="395" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A395">
+        <v>394</v>
+      </c>
+      <c r="B395">
+        <v>32.768000000000001</v>
+      </c>
+      <c r="C395">
+        <v>32.588999999999999</v>
+      </c>
+      <c r="D395" s="2">
+        <v>32.536999999999999</v>
+      </c>
+      <c r="E395">
+        <v>32.645000000000003</v>
+      </c>
+      <c r="F395">
+        <v>32.572000000000003</v>
+      </c>
+    </row>
+    <row r="396" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A396">
+        <v>395</v>
+      </c>
+      <c r="B396">
+        <v>32.78</v>
+      </c>
+      <c r="C396">
+        <v>32.587000000000003</v>
+      </c>
+      <c r="D396">
+        <v>32.534999999999997</v>
+      </c>
+      <c r="E396">
+        <v>32.646999999999998</v>
+      </c>
+      <c r="F396">
+        <v>32.573</v>
+      </c>
+    </row>
+    <row r="397" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A397">
+        <v>396</v>
+      </c>
+      <c r="B397">
+        <v>32.779000000000003</v>
+      </c>
+      <c r="C397">
+        <v>32.588000000000001</v>
+      </c>
+      <c r="D397">
+        <v>32.534999999999997</v>
+      </c>
+      <c r="E397">
+        <v>32.646000000000001</v>
+      </c>
+      <c r="F397">
+        <v>32.572000000000003</v>
+      </c>
+    </row>
+    <row r="398" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A398">
+        <v>397</v>
+      </c>
+      <c r="B398">
+        <v>32.781999999999996</v>
+      </c>
+      <c r="C398">
+        <v>32.584000000000003</v>
+      </c>
+      <c r="D398">
+        <v>32.534999999999997</v>
+      </c>
+      <c r="E398">
+        <v>32.643999999999998</v>
+      </c>
+      <c r="F398">
+        <v>32.576000000000001</v>
+      </c>
+    </row>
+    <row r="399" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A399">
+        <v>398</v>
+      </c>
+      <c r="B399">
+        <v>32.78</v>
+      </c>
+      <c r="C399">
+        <v>32.590000000000003</v>
+      </c>
+      <c r="D399">
+        <v>32.533999999999999</v>
+      </c>
+      <c r="E399">
+        <v>32.646000000000001</v>
+      </c>
+      <c r="F399">
+        <v>32.576000000000001</v>
+      </c>
+    </row>
+    <row r="400" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A400">
+        <v>399</v>
+      </c>
+      <c r="B400">
+        <v>32.789000000000001</v>
+      </c>
+      <c r="C400">
+        <v>32.588999999999999</v>
+      </c>
+      <c r="D400">
+        <v>32.531999999999996</v>
+      </c>
+      <c r="E400">
+        <v>32.646999999999998</v>
+      </c>
+      <c r="F400">
+        <v>32.573999999999998</v>
+      </c>
+    </row>
+    <row r="401" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A401">
+        <v>400</v>
+      </c>
+      <c r="B401">
+        <v>32.780999999999999</v>
+      </c>
+      <c r="C401">
+        <v>32.590000000000003</v>
+      </c>
+      <c r="D401">
+        <v>32.533000000000001</v>
+      </c>
+      <c r="E401">
+        <v>32.646000000000001</v>
+      </c>
+      <c r="F401">
+        <v>32.578000000000003</v>
+      </c>
+    </row>
+    <row r="402" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A402">
+        <v>401</v>
+      </c>
+      <c r="B402">
+        <v>32.779000000000003</v>
+      </c>
+      <c r="C402">
+        <v>32.587000000000003</v>
+      </c>
+      <c r="D402">
+        <v>32.533000000000001</v>
+      </c>
+      <c r="E402">
+        <v>32.646000000000001</v>
+      </c>
+      <c r="F402">
+        <v>32.575000000000003</v>
+      </c>
+    </row>
+    <row r="403" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A403">
+        <v>402</v>
+      </c>
+      <c r="B403">
+        <v>32.768999999999998</v>
+      </c>
+      <c r="C403">
+        <v>32.587000000000003</v>
+      </c>
+      <c r="D403">
+        <v>32.533999999999999</v>
+      </c>
+      <c r="E403">
+        <v>32.646999999999998</v>
+      </c>
+      <c r="F403">
+        <v>32.575000000000003</v>
+      </c>
+    </row>
+    <row r="404" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A404">
+        <v>403</v>
+      </c>
+      <c r="B404">
+        <v>32.787999999999997</v>
+      </c>
+      <c r="C404">
+        <v>32.590000000000003</v>
+      </c>
+      <c r="D404">
+        <v>32.533000000000001</v>
+      </c>
+      <c r="E404">
+        <v>32.65</v>
+      </c>
+      <c r="F404">
+        <v>32.575000000000003</v>
+      </c>
+    </row>
+    <row r="405" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A405">
+        <v>404</v>
+      </c>
+      <c r="B405">
+        <v>32.765999999999998</v>
+      </c>
+      <c r="C405">
+        <v>32.591999999999999</v>
+      </c>
+      <c r="D405">
+        <v>32.531999999999996</v>
+      </c>
+      <c r="E405">
+        <v>32.649000000000001</v>
+      </c>
+      <c r="F405">
+        <v>32.578000000000003</v>
+      </c>
+    </row>
+    <row r="406" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A406">
+        <v>405</v>
+      </c>
+      <c r="B406">
+        <v>32.777000000000001</v>
+      </c>
+      <c r="C406">
+        <v>32.588000000000001</v>
+      </c>
+      <c r="D406">
+        <v>32.531999999999996</v>
+      </c>
+      <c r="E406">
+        <v>32.65</v>
+      </c>
+      <c r="F406">
+        <v>32.573999999999998</v>
+      </c>
+    </row>
+    <row r="407" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A407">
+        <v>406</v>
+      </c>
+      <c r="B407" s="3">
+        <v>32.804000000000002</v>
+      </c>
+      <c r="C407">
+        <v>32.588000000000001</v>
+      </c>
+      <c r="D407">
+        <v>32.533999999999999</v>
+      </c>
+      <c r="E407">
+        <v>32.649000000000001</v>
+      </c>
+      <c r="F407">
+        <v>32.576000000000001</v>
+      </c>
+    </row>
+    <row r="408" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A408">
+        <v>407</v>
+      </c>
+      <c r="B408">
+        <v>32.777000000000001</v>
+      </c>
+      <c r="C408">
+        <v>32.588999999999999</v>
+      </c>
+      <c r="D408">
+        <v>32.531999999999996</v>
+      </c>
+      <c r="E408">
+        <v>32.651000000000003</v>
+      </c>
+      <c r="F408">
+        <v>32.575000000000003</v>
+      </c>
+    </row>
+    <row r="409" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A409">
+        <v>408</v>
+      </c>
+      <c r="B409">
+        <v>32.792000000000002</v>
+      </c>
+      <c r="C409">
+        <v>32.588000000000001</v>
+      </c>
+      <c r="D409">
+        <v>32.533000000000001</v>
+      </c>
+      <c r="E409">
+        <v>32.649000000000001</v>
+      </c>
+      <c r="F409">
+        <v>32.576000000000001</v>
+      </c>
+    </row>
+    <row r="410" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A410">
+        <v>409</v>
+      </c>
+      <c r="B410">
+        <v>32.781999999999996</v>
+      </c>
+      <c r="C410">
+        <v>32.590000000000003</v>
+      </c>
+      <c r="D410">
+        <v>32.533000000000001</v>
+      </c>
+      <c r="E410">
+        <v>32.649000000000001</v>
+      </c>
+      <c r="F410">
+        <v>32.576000000000001</v>
+      </c>
+    </row>
+    <row r="411" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A411">
+        <v>410</v>
+      </c>
+      <c r="B411">
+        <v>32.776000000000003</v>
+      </c>
+      <c r="C411">
+        <v>32.591000000000001</v>
+      </c>
+      <c r="D411">
+        <v>32.533999999999999</v>
+      </c>
+      <c r="E411">
+        <v>32.648000000000003</v>
+      </c>
+      <c r="F411">
+        <v>32.576000000000001</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
